--- a/data/mapping/diagnosis_kdrg44_mapping.xlsx
+++ b/data/mapping/diagnosis_kdrg44_mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뇌경색</t>
+          <t>허혈 뇌졸중 및 기타 비출혈성 뇌졸중</t>
         </is>
       </c>
     </row>
@@ -2117,6 +2117,2970 @@
       <c r="B165" t="inlineStr">
         <is>
           <t>신경계 신생물(기타)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>바이러스성 및 기타 명시된 장감염</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 &gt; 2499g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>뇌경색증을 유발하지 않은 뇌전동맥의 폐쇄 및 협착</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>일과성 뇌 허혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>거미막하출혈</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>뇌기저부 수술(외상 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>악성 신생물 이외의 병태에 대한 치료후 추적검사</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>기타 HIV</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>결절성 다발동맥염 및 관련 병태</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>가와사키병</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>안면신경장애</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>바이러스성 수막염</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>의심되는 질병 및 병태를 위한 의학적 관찰 및 평가, 배제된</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>호흡기결핵</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>손가락 및 발가락의 후천변형</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>생검을 포함한 골과 관절의 진단적 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 경련</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>뇌진탕</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>기관지 및 폐의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>기관지확장증</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>골괴사</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>생검을 포함한 골과 관절의 진단적 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>난소, 난관 및 넓은인대의 비염증성 장애</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>월경장애 및 기타 여성생식기계 장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>고체 및 액체에 의한 폐렴</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>수면무호흡증후군</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>만성 콩팥병</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>신투석 치료를 위한 입원</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>기타 빈혈</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1250-1499g(중요 수술 미시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>윤활막염 및 힘줄윤활막염</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>생검을 포함한 골과 관절의 진단적 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>기타 변형성 등병증</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Spinal Fusion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>U07의 응급사용</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>미만성 폐질환</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>뇌경색증을 유발하지 않은 대뇌동맥의 폐쇄 및 협착</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>일과성 뇌 허혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 기타 관절장애</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>생검을 포함한 골과 관절의 진단적 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>자궁경부를 제외한 자궁의 기타 비염증성 장애</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>월경장애 및 기타 여성생식기계 장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>급성 림프절염</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>화농성 관절염</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>생검을 포함한 골과 관절의 진단적 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>피부 및 피하조직의 모낭낭</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>기타 단순 피부 질환</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>위염 및 십이지장염</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>전음성 및 감각신경성 청력소실</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>하지의 양측 또는 복수 주요 관절 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>심장중격의 선천기형</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>견갑대의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>췌장의 기타 질환</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>결장경 시술</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>비화농성 중이염</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>청각장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>자반 및 기타 출혈성 병태</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>난소의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>여성생식기계 악성종양(방사선치료를 받은 경우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 생체역학적 병변</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>비외과적 경부 및 척추 상태(통증관리 및 척수강조영 실시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>하지의 정맥류</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1500-1999g(중요 수술 미시행, 다발성 주요 문제 동반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>기타 만성 폐쇄성 폐질환</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>만성 폐색성 폐질환</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>호흡 및 소화기관의 이차성 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>소화기 악성종양(방사선치료를 받은 경우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>목부위의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>비외과적 경부 및 척추 상태(통증관리 및 척수강조영 실시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>어깨 및 위팔 부위의 근육 및 힘줄의 손상</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>십자인대 수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>신우를 제외한 신장의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>신장 및 요로 신생물(방사선치료를 받은 경우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>고관절증</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>단단성형술(수족지 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>다발골수종 및 악성 형질세포신생물</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>신생아, 입원시 체중 1250-1499g(중요 수술 미시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>근육의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>항뇌전증제, 진정제-수면제 및 항파킨슨제에 의한 중독</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>결합조직 및 기타 연조직의 기타 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Other Shoulder Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>방광염</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Lower Urinary Tract Infections, Age ＜65 L64313 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 소화계통의 처치후 장애</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Other Gastrointestinal Symptoms G67302 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>여성생식기탈출</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Menstrual and Other Female Reproductive N62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>동맥 및 세동맥의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Percutaneous Embolization for Arteriovenous Malformation except Head and Neck</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>식도의 기타 질환</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>독성간질환</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Endoscopic Procedures for Bleeding Varices</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>기타 심장부정맥</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Bradycardia F74102 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>피부의 농양, 종기 및 큰종기</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Cellulitis, Age ≤18 J65012 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>급성 A형간염</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis with Complications H66100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명의 소화기관의 제자리암종</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Other Diseases of the Eye, Age ≤18 C63011 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>복막염</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>시각장애</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Other Diseases of the Eye, Age ≤18 C63011 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>자궁경부의 이형성</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Menstrual and Other Female Reproductive N62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>기타 부위의 정맥류</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Varicose Vein F69100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>기타 및 부위불명 소화기관의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Ear, Nose, Mouth and Throat Malignancy D60203 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>골 및 관절연골의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>고환염 및 부고환염</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Inflammation of the Male Reproductive M62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명 부위의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Digestive Malignancy with Radiation G60103 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>윤활막 및 힘줄의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명 부위의 이차성 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CNS Stereotactic Procedures in Brain Tumor and Other Creation of Lesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>하부요로의 결석</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Urinary Stones and Obstruction L65003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>기타 특정 관절장애</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>자궁체부의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Laparoscopic Uterus Procedures for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>단핵구성 백혈병</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>구역 및 구토</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Other Gastrointestinal Symptoms G67302 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>골수형성이상증후군</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Connective Tissue Malignancy, Including I65311 W Catastrophic or Severe or Moderate CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>상세불명의 혈뇨</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Signs and L66100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>아래다리의 표재성 손상</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Injuries to Shoulder, Arm, Elbow, Knee, I75010 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>방실차단 및 좌각차단</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Other Cardiac Arrest, Unspecified F65201 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>이식장치의 조정 및 관리를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Other Circulatory System Diseases F80003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>뇌전증</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Simple Cerebral Aneurysm Procedures with Stroke</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>섬유모세포장애</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>기타 관절증</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 기타 연조직장애</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Neuropathic Pain and Autonomic Nerve B71803 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>병적 골절을 동반한 골다공증</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>비특이성 림프절염</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Abdominal Pain or Mesenteric Adenitis G66003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>기타 비감염성 위장염 및 결장염</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Enteritis, Age ≤18 G67113 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 정신작용제에 의한 중독</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>폐색전증</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Pulmonary Embolism E60002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>기타 외과적 추적치료를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Follow-Up Care after Completed Treatment Z62000 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명의 원인에 의한 수막염</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Non-Specific Meningitis B73401 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명 부위의 제자리암종</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Other Diseases of the Eye, Age ≤18 C63011 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>음식 및 수액 섭취에 관계된 증상 및 징후</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Other Metabolic Disorders, Age ≤18 K63010 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>기타 형태의 마이코박테리아에 의한 감염</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Respiratory Tuberculosis E61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>목부위의 신경 및 척수의 손상</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders without Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>위-식도역류병</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Esophagitis and Gastroduodenitis, Age G67211 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>인지기능 및 자각에 관련된 기타 증상 및 징후</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Other HIV S64001 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 호흡부전</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>자궁경부의 제자리암종</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Malignancy of Male Reproductive System M60101 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 처치후 근골격장애</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Non-Surgical Neck and Back Conditions I68113 W Catastrophic CC 중증도</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>부위의 명시가 없는 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 2000-2499g P66100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>유방의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Mastectomy except Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>목의 골절</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>기타 질환 및 장애에 대한 특수선별검사</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Other Factors Influencing Health Status Z64002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>삼차신경의 장애</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Cranial Nerve Disorders B71503 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 간부전</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Endoscopic Procedures for Bleeding Varices</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>식도의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>배꼽탈장</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Other Digestive system Diseases G68902 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>림프, 조혈 및 관련 조직의 행동양식 불명 및 미상의 기타 신생물</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Sigmoidoscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>기타 무형성빈혈</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Paranasal Sinus Infections and D68001 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>요관의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Neoplasms with L63100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>비류마티스성 대동맥판장애</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Valvular Diseases F73002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>림프성 백혈병</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>간의 기타 질환</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Endoscopic Procedures for Bleeding Varices</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>기타 신세뇨관-간질질환</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Acute Renal Failure, Hemodialysis and L60311 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>음낭수종 및 정액류</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Inflammation of the Male Reproductive M62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>모소낭</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Cellulitis, Age ≤18 J65012 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>기타 비독성 고이터</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>등통증</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Spinal Fusion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>악성 신생물에 대한 치료후 추적검사</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Follow-Up Care after Completed Treatment Z62000 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>마비성 사시</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Neurological and Vascular Diseases of the C61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 외과적 및 내과적 치료의 기타 합병증</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases F69203 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>주입, 수혈 및 치료용 주사에 따른 합병증</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Pulmonary Embolism E60002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>얼굴 및 목의 기타 선천기형</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Dental Restorations</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>신생물에 대한 특수선별검사</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Other Factors Influencing Health Status Z64002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>외이염</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>External Ear Infections and Inflammations D63000 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>기타 다발신경병증</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Peripheral Nerve Disorders B71702 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>복벽탈장</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Crohn’s disease G64101 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명의 흉곽내기관의 손상</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Major Chest Trauma, Age ＜65 E68112 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>심장박동의 이상</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Hypothermia Therapy F65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>식품으로 섭취한 기타 유해물질의 독성효과</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1500-1999g P65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>기타 골부착부병증</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>중이 및 호흡계통의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>항문 및 항문관의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Rectal Resection, Transanal or Transsacral Approach for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>비뇨기관의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Neoplasms with L63100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>성형수술을 포함한 추적치료를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Mastectomy except Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>기타 신체구조의 진단영상검사상 이상소견</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>철결핍빈혈</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1500-1999g P65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>골연속성의 장애</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>고관절의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>뇌 및 중추신경계통의 행동양식 불명 또는 미상의 신생물</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>CNS Stereotactic Procedures in Brain Tumor and Other Creation of Lesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Syncope and Collapse F77002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>기타 말초혈관질환</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases F69203 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>머리의 표재성 손상</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Hyphema and Medically Managed Trauma C62001 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>갑상선염</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>기타 윤활낭병증</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>손목 및 손부위의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Major Wrist and Hand Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>급성 부비동염</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>헤르페스바이러스[단순헤르페스] 감염</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>기타 전신 증상 및 징후</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>비뇨 및 골반 기관의 손상</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Unilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>기타 내부 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Other Nervous System Disorders B81402 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>만성 바이러스간염</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Other Hepatitis with Complications H67101 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>비뇨생식기 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Kidney and Upper Urinary Tract Infections L64112 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>기타 이상 자궁 및 질 출혈</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Menstrual and Other Female Reproductive N62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>재활처치를 포함한 치료를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Rehabilitation, Age ≤18 Z60010 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 쇼크</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders without Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>구강 및 소화기관의 행동양식 불명 또는 미상의 신생물</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>기타 마비증후군</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Excision of Intraspinal Lesion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>팔꿈치의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Elbow and Forearm Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>연골의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Other Respiratory System Diseases E77303 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>질 및 외음부의 기타 염증</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections N61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>난관염 및 난소염</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections N61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>여성생식기관 및 월경주기와 관련된 통증 및 기타 병태</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Menstrual and Other Female Reproductive N62003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>피부의 기타 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Other Diseases of the Eye, Age ≤18 C63011 W Catastrophic or Severe or Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>비뇨기관의 행동양식 불명 또는 미상의 신생물</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Nervous System Neoplasm without B63311 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>호흡의 이상</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Allergic Rhinitis D69102 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>기타 특정 관절병증</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>복막의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Diseases of Peritoneum G68201 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>기타 대사장애</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Transcatheter Closure of Atrial Septal Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>피부의 악성 흑색종</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders without Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>장의 기타 선천기형</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>정맥염 및 혈전정맥염</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Percutaneous Procedures of Deep Vein Thrombosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>백혈구의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1500-1999g P65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>수막의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>CNS Stereotactic Procedures in Brain Tumor and Other Creation of Lesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>바이러스수막염</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Viral Meningitis B74001 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>자연유산</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>High Risk Vaginal Delivery(Primiparity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>근육의 석회화 및 골화</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 기타 주로 성행위로 전파되는 질환</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Other Minor Skin Diseases J70003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>후천성 용혈성 빈혈</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Non-Infectious Kidney Diseases with L62112 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>혈관운동성 및 알레르기성 비염</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 사춘기의 장애</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Pleural Effusion Drainage</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>악성 면역증식성 질환</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>달리 분류된 만성 질환에서의 빈혈</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1500-1999g P65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>통풍</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>욕창궤양 및 압박부위</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Flap for Skin Ulcer or Cellulitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>골수성 백혈병</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>수막의 행동양식 불명 또는 미상의 신생물</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>CNS Stereotactic Procedures in Brain Tumor and Other Creation of Lesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>비뇨생식관의 이물</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Other Kidney and Urinary Tract Diseases L68003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>기타 결합조직 및 연조직의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>자궁경부를 제외한 자궁의 염증성 질환</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections N61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>중추신경계통의 기타 탈수초질환</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Simple Cerebral Aneurysm Procedures with Stroke</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>투석을 포함한 치료를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Chronic Renal Failure, Peritoneal Dialysis, L61112 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>기타 갑상선기능저하증</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>외이의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Inner and Middle Ear Infections and D62201 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>코용종</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>발목 및 발의 화상 및 부식</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>비류마티스성 승모판장애</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Valvular Diseases F73002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>전신항생제에 의한 중독</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Neonate, Admission Weight 1250-1499g P64100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>중이의 진주종</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Inner and Middle Ear Infections and D62100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>내부로 섭취된 물질에 의한 피부염</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Other Moderate Skin Diseases J69003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>유방의 선천기형</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Mastectomy except Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>기타 관절염</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>피부의 비대성 장애</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Other Minor Skin Diseases J70003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>입술 및 구강점막의 기타 질환</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>혈청검사양성 류마티스관절염</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Other Interstitial Lung Disease E75301 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>후각 및 미각 장애</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Other Nervous System Disorders B81402 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>대동맥동맥류 및 박리</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Repair of Aneurysm or Coarctation of Aorta with Rupture, with Pump Oxygenator</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>강직척추염</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Spinal Fusion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>기타 불안장애</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Anxiety Disorders and Sleep Disorders U65002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>뼈의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>우울에피소드</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Affective Disorders, Age ≥65 U63021 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>안와의 장애</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Acute and Major Eye Infections, Age ＜65 C60010 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>소장의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명의 비뇨기관의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Neoplasms with L63100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>정맥의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases F69203 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 신경계통의 처치후 장애</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Headache B78003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>기타 류마티스관절염</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>기타 내부기관의 화상 및 부식</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>달리 분류된 질환에서의 신경계통의 기타 퇴행장애</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Atypical Parkinsonism B64201 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>림프절의 이차성 및 상세불명의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>티아민결핍</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Severe Nutritional Disturbance K62002 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>위공장궤양</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Gastroscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>갑상선독증[갑상선기능항진증]</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Long-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>기타 여성골반염증질환</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections N61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>발목 및 발 부위의 신경의 손상</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Injury of Peripheral Nerve B70200 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>사용, 과용 및 압박에 관련된 연조직장애</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>뇌의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Spinal Fusion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 귀의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Hearing Impairment, Age ≤18 D65010 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>아래팔 부위의 근육 및 힘줄의 손상</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Elbow and Forearm Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>복부, 아래등 및 골반 부위의 신경 및 허리척수의 손상</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Evacuation of Hematoma related to Trauma, Other Intracerebral Hemorrhage</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>심장정지</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Hypothermia Therapy F65100 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>복강내기관의 손상</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Other Major Digestive system Diseases G68801 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>뼈의 파젯병[변형성 골염]</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>피부 및 피하조직의 국소적 부기, 종괴 및 덩이</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Spinal Fusion with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>자궁경부의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Laparoscopic Cervix, Vagina and Vulva Procedures for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>엉덩이 및 대퇴 부위의 근육 및 힘줄의 손상</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Hip and Femur Procedures, Bilateral or Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>엉덩이 및 대퇴의 표재성 손상</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Femoral Neck Fracture I62202 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>손목 및 손 부위의 근육 및 힘줄의 손상</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Major Wrist and Hand Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>남성생식기관의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Neoplasms with L63203 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>근긴장이상</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Dystonia B65201 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>달리 분류된 질환에서의 뇌신경장애</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Injury of Cranial Nerve and Disease of B71300 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>알려진 또는 의심되는 불균형에 대한 산모관리</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>High Risk Cesarean Delivery(Single Birth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>보행과 이동의 이상</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Other Spinal Procedures with Myelopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>출산장소에 따른 생존출생</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Minor Breast Procedures using Vaccum-Assisted Biopsy Device</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>결합조직의 기타 전신침범</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Other Connective Tissue Diseases, I66712 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>인공개구에 대한 관리를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Other Respiratory System Diseases E77303 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>기능검사의 이상결과</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Tracheostomy for Face, Mouth and Neck Disorders with Short-Term Ventilator</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>달리 분류된 질환에서의 다발신경병증</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Diabetic Neuropathy B71102 W Catastrophic or Severe CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>바르톨린선의 질환</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections N61003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>급성 심근염</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Other Circulatory System Diseases F80003 W Catastrophic CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 비뇨생식계통의 처치후 장애</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Acute Renal Failure, Continuous Renal L60110 중증도 구분 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>혈액화학의 기타 이상소견</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>징후 및 증상</t>
         </is>
       </c>
     </row>
